--- a/output/roomself_excel/8507.xlsx
+++ b/output/roomself_excel/8507.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>97933</v>
+        <v>139977</v>
       </c>
       <c r="D2" t="n">
-        <v>2504</v>
+        <v>3048</v>
       </c>
       <c r="E2" t="n">
-        <v>352</v>
+        <v>453</v>
       </c>
       <c r="F2" t="n">
-        <v>340</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3">
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>477862</v>
+        <v>291345</v>
       </c>
       <c r="D3" t="n">
-        <v>7280</v>
+        <v>4352</v>
       </c>
       <c r="E3" t="n">
-        <v>894</v>
+        <v>567</v>
       </c>
       <c r="F3" t="n">
-        <v>567</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>128778</v>
+        <v>97933</v>
       </c>
       <c r="D4" t="n">
-        <v>3004</v>
+        <v>2504</v>
       </c>
       <c r="E4" t="n">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="F4" t="n">
-        <v>33</v>
+        <v>340</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28055</v>
+        <v>128778</v>
       </c>
       <c r="D5" t="n">
-        <v>1344</v>
+        <v>3004</v>
       </c>
       <c r="E5" t="n">
-        <v>217</v>
+        <v>338</v>
       </c>
       <c r="F5" t="n">
-        <v>192</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>47586</v>
+        <v>113646</v>
       </c>
       <c r="D6" t="n">
-        <v>1748</v>
+        <v>2740</v>
       </c>
       <c r="E6" t="n">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="F6" t="n">
-        <v>208</v>
+        <v>315</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>79842</v>
+        <v>112926</v>
       </c>
       <c r="D7" t="n">
-        <v>2576</v>
+        <v>2692</v>
       </c>
       <c r="E7" t="n">
-        <v>446</v>
+        <v>387</v>
       </c>
       <c r="F7" t="n">
-        <v>221</v>
+        <v>352</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>29601</v>
+        <v>47586</v>
       </c>
       <c r="D8" t="n">
-        <v>1400</v>
+        <v>1748</v>
       </c>
       <c r="E8" t="n">
-        <v>143</v>
+        <v>206</v>
       </c>
       <c r="F8" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9">
@@ -620,14 +620,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>14300</v>
+        <v>21726</v>
       </c>
       <c r="D9" t="n">
-        <v>972</v>
+        <v>1180</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>113646</v>
+        <v>46540</v>
       </c>
       <c r="D10" t="n">
-        <v>2740</v>
+        <v>1952</v>
       </c>
       <c r="E10" t="n">
-        <v>436</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>315</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>112926</v>
+        <v>46719</v>
       </c>
       <c r="D11" t="n">
-        <v>2692</v>
+        <v>1760</v>
       </c>
       <c r="E11" t="n">
-        <v>387</v>
+        <v>179</v>
       </c>
       <c r="F11" t="n">
-        <v>352</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12">
@@ -686,17 +686,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>46719</v>
+        <v>29601</v>
       </c>
       <c r="D12" t="n">
-        <v>1760</v>
+        <v>1400</v>
       </c>
       <c r="E12" t="n">
-        <v>179</v>
+        <v>143</v>
       </c>
       <c r="F12" t="n">
         <v>33</v>
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21726</v>
+        <v>16125</v>
       </c>
       <c r="D13" t="n">
-        <v>1180</v>
+        <v>1040</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -730,20 +730,64 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16125</v>
+        <v>28055</v>
       </c>
       <c r="D14" t="n">
-        <v>1040</v>
+        <v>1344</v>
       </c>
       <c r="E14" t="n">
-        <v>153</v>
+        <v>217</v>
       </c>
       <c r="F14" t="n">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>79842</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2576</v>
+      </c>
+      <c r="E15" t="n">
+        <v>238</v>
+      </c>
+      <c r="F15" t="n">
         <v>33</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>14300</v>
+      </c>
+      <c r="D16" t="n">
+        <v>972</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/8507.xlsx
+++ b/output/roomself_excel/8507.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,12 +495,20 @@
       <c r="D2" t="n">
         <v>3048</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>453</v>
       </c>
-      <c r="F2" t="n">
-        <v>33</v>
-      </c>
+      <c r="G2" t="n">
+        <v>33</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +525,20 @@
       <c r="D3" t="n">
         <v>4352</v>
       </c>
-      <c r="E3" t="n">
-        <v>567</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>33</v>
-      </c>
+        <v>556</v>
+      </c>
+      <c r="G3" t="n">
+        <v>33</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,11 +555,27 @@
       <c r="D4" t="n">
         <v>2504</v>
       </c>
-      <c r="E4" t="n">
-        <v>352</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>340</v>
+        <v>319</v>
+      </c>
+      <c r="G4" t="n">
+        <v>33</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>307</v>
+      </c>
+      <c r="J4" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="5">
@@ -541,12 +593,20 @@
       <c r="D5" t="n">
         <v>3004</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>338</v>
       </c>
-      <c r="F5" t="n">
-        <v>33</v>
-      </c>
+      <c r="G5" t="n">
+        <v>33</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,11 +623,27 @@
       <c r="D6" t="n">
         <v>2740</v>
       </c>
-      <c r="E6" t="n">
-        <v>436</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>315</v>
+        <v>403</v>
+      </c>
+      <c r="G6" t="n">
+        <v>33</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>282</v>
+      </c>
+      <c r="J6" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="7">
@@ -585,11 +661,27 @@
       <c r="D7" t="n">
         <v>2692</v>
       </c>
-      <c r="E7" t="n">
-        <v>387</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>352</v>
+        <v>354</v>
+      </c>
+      <c r="G7" t="n">
+        <v>33</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>319</v>
+      </c>
+      <c r="J7" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="8">
@@ -607,12 +699,20 @@
       <c r="D8" t="n">
         <v>1748</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>206</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>42</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +729,12 @@
       <c r="D9" t="n">
         <v>1180</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +751,12 @@
       <c r="D10" t="n">
         <v>1952</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +773,20 @@
       <c r="D11" t="n">
         <v>1760</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>179</v>
       </c>
-      <c r="F11" t="n">
-        <v>33</v>
-      </c>
+      <c r="G11" t="n">
+        <v>33</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +803,20 @@
       <c r="D12" t="n">
         <v>1400</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>143</v>
       </c>
-      <c r="F12" t="n">
-        <v>33</v>
-      </c>
+      <c r="G12" t="n">
+        <v>33</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +833,20 @@
       <c r="D13" t="n">
         <v>1040</v>
       </c>
-      <c r="E13" t="n">
-        <v>153</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>33</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="G13" t="n">
+        <v>33</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,11 +863,27 @@
       <c r="D14" t="n">
         <v>1344</v>
       </c>
-      <c r="E14" t="n">
-        <v>217</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>192</v>
+        <v>181</v>
+      </c>
+      <c r="G14" t="n">
+        <v>37</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>155</v>
+      </c>
+      <c r="J14" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -761,12 +901,20 @@
       <c r="D15" t="n">
         <v>2576</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
         <v>238</v>
       </c>
-      <c r="F15" t="n">
-        <v>33</v>
-      </c>
+      <c r="G15" t="n">
+        <v>33</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +931,12 @@
       <c r="D16" t="n">
         <v>972</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
